--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10600"/>
+    <workbookView windowWidth="21000" windowHeight="10000"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>RecipeID</t>
+  </si>
   <si>
     <t>DishList</t>
   </si>
@@ -42,6 +45,9 @@
   </si>
   <si>
     <t>CookResult</t>
+  </si>
+  <si>
+    <t>OnCookBuffList</t>
   </si>
   <si>
     <t>炒番茄</t>
@@ -69,14 +75,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -532,148 +531,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -998,15 +997,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="14.4166666666667" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="14.4166666666667" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="7" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1022,56 +1021,80 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
+      <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>201</v>
       </c>
+      <c r="G2">
+        <v>11001</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>202</v>
       </c>
+      <c r="G3">
+        <v>11001</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
         <v>203</v>
+      </c>
+      <c r="G4">
+        <v>11001</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="10000"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
@@ -1045,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>11001</v>
@@ -1068,7 +1068,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>11001</v>
@@ -1091,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>203</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>11001</v>

--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unity\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC345A74-4581-4234-BA9A-13543339A166}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D5B09-A2D9-4121-A570-4A6103AEBD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-405" yWindow="1193" windowWidth="14400" windowHeight="8182" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>RecipeID</t>
   </si>
@@ -59,13 +59,39 @@
   </si>
   <si>
     <t>cookTypeIconPath</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>土豆咖喱牛腩</t>
+  </si>
+  <si>
+    <t>葱鸡腿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7|8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8|8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +101,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -101,8 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -378,15 +416,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="14.4140625" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="18.5" customWidth="1"/>
+    <col min="6" max="7" width="18.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -412,7 +450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -438,7 +476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -464,7 +502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -487,6 +525,84 @@
         <v>11001</v>
       </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>11001</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>11001</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>11001</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unity\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D5B09-A2D9-4121-A570-4A6103AEBD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95654D55-2F3F-4679-976A-E4CBBEF4F907}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-405" yWindow="1193" windowWidth="14400" windowHeight="8182" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-410" yWindow="1190" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>RecipeID</t>
   </si>
@@ -85,6 +85,15 @@
   <si>
     <t>6|6</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/fishdish_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/beafsoup_icon.png</t>
+  </si>
+  <si>
+    <t>Assets/Sprites/Icons/Onionchicken_icon.png</t>
   </si>
 </sst>
 </file>
@@ -135,10 +144,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -417,14 +429,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.3984375" customWidth="1"/>
+    <col min="3" max="3" width="14.4140625" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="18.46484375" customWidth="1"/>
+    <col min="6" max="7" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,7 +462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -476,7 +488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -502,7 +514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -528,7 +540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -550,11 +562,11 @@
       <c r="G5">
         <v>11001</v>
       </c>
-      <c r="H5">
-        <v>0</v>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -576,11 +588,11 @@
       <c r="G6">
         <v>11001</v>
       </c>
-      <c r="H6">
-        <v>0</v>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -602,8 +614,8 @@
       <c r="G7">
         <v>11001</v>
       </c>
-      <c r="H7">
-        <v>0</v>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95654D55-2F3F-4679-976A-E4CBBEF4F907}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDE7ACC-B56A-4B2E-81D2-CFBB6B920935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-410" yWindow="1190" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>RecipeID</t>
   </si>
@@ -41,21 +46,6 @@
   </si>
   <si>
     <t>OnCookBuffList</t>
-  </si>
-  <si>
-    <t>炒番茄</t>
-  </si>
-  <si>
-    <t>炒鸡蛋</t>
-  </si>
-  <si>
-    <t>1|2</t>
-  </si>
-  <si>
-    <t>番茄炒鸡蛋</t>
-  </si>
-  <si>
-    <t>5|5</t>
   </si>
   <si>
     <t>cookTypeIconPath</t>
@@ -124,12 +114,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -144,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -153,6 +149,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -428,15 +426,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.4140625" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" style="4" customWidth="1"/>
     <col min="6" max="7" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +448,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -459,168 +458,90 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
+        <v>10</v>
+      </c>
+      <c r="F2">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
       </c>
       <c r="G2">
         <v>11001</v>
       </c>
-      <c r="H2">
-        <v>0</v>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>11001</v>
       </c>
-      <c r="H3">
-        <v>0</v>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>11001</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>11001</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>11001</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>11001</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDE7ACC-B56A-4B2E-81D2-CFBB6B920935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB587041-9F35-4EA4-9837-80E127D6A217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-100" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>RecipeID</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>CookType</t>
-  </si>
-  <si>
-    <t>CookTime</t>
   </si>
   <si>
     <t>CookResult</t>
@@ -69,21 +66,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>8|8</t>
+    <t>Icons/fishdish_icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6|6</t>
+    <t>Icons/beafsoup_icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Sprites/Icons/fishdish_icon.png</t>
-  </si>
-  <si>
-    <t>Assets/Sprites/Icons/beafsoup_icon.png</t>
-  </si>
-  <si>
-    <t>Assets/Sprites/Icons/Onionchicken_icon.png</t>
+    <t>Icons/Onionchicken_icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -114,18 +106,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -140,17 +126,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -426,16 +407,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.375" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" style="4" customWidth="1"/>
-    <col min="6" max="7" width="18.5" customWidth="1"/>
+    <col min="5" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,7 +429,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -457,11 +438,8 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>4</v>
       </c>
@@ -469,74 +447,65 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" s="4">
-        <v>10</v>
+      <c r="E2">
+        <v>12</v>
       </c>
       <c r="F2">
+        <v>11001</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2">
-        <v>11001</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3">
         <v>13</v>
       </c>
       <c r="F3">
+        <v>11001</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3">
-        <v>11001</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4">
         <v>14</v>
       </c>
       <c r="F4">
+        <v>11001</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="G4">
-        <v>11001</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB587041-9F35-4EA4-9837-80E127D6A217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B55B6B-FC74-4363-8869-DD35A7E6EFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-100" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>RecipeID</t>
   </si>
@@ -75,6 +70,14 @@
   </si>
   <si>
     <t>Icons/Onionchicken_icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|9|7|8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满汉全席</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -82,17 +85,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -100,10 +103,25 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,12 +144,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -407,16 +427,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="24.875" customWidth="1"/>
+    <col min="7" max="7" width="24.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>4</v>
       </c>
@@ -462,7 +482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>5</v>
       </c>
@@ -485,7 +505,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>6</v>
       </c>
@@ -506,6 +526,26 @@
       </c>
       <c r="G4" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>11001</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/Recipe.xlsx
+++ b/Assets/Configs/Recipe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B55B6B-FC74-4363-8869-DD35A7E6EFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21612B00-9359-48AF-AC7F-64CDFE96BA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>RecipeID</t>
   </si>
@@ -78,6 +78,10 @@
   </si>
   <si>
     <t>满汉全席</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/FullCombo_icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,8 +123,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -144,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -152,6 +155,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -430,7 +436,7 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="14.3984375" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" style="4" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="24.8984375" customWidth="1"/>
@@ -443,7 +449,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -466,7 +472,7 @@
       <c r="B2">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D2">
@@ -489,7 +495,7 @@
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D3">
@@ -512,7 +518,7 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D4">
@@ -535,7 +541,7 @@
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D5">
@@ -546,6 +552,9 @@
       </c>
       <c r="F5">
         <v>11001</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
